--- a/Data Base/Global Templates/Pre Cast RCC Ring for ARS Pit.xlsx
+++ b/Data Base/Global Templates/Pre Cast RCC Ring for ARS Pit.xlsx
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Providing and laying in position cement concrete of specified grade excluding the cost of centering and shuttering - All work up to plinth level: 1:2:4 (cement : 2 coarse sand (zone-III) : 4 graded stone aggregate 20 mm nominal size) (Code: 4.1.3)</t>
-  </si>
-  <si>
     <t>Steel reinforcement for R.C.C work including straightening, cutting, bending, placing in position and binding all complete upto plinth level Mild steel and Medium Tensile steel bars (Code: 5.22.1)</t>
   </si>
   <si>
@@ -38,18 +35,28 @@
   </si>
   <si>
     <t>Hire charges of Concrete Mixer 0.25 to 0.40 cum with Hopper (Code: 0002 - Water Charge and CPOH Added)</t>
+  </si>
+  <si>
+    <t>Providing and laying in position specified grade of RCC, excluding the cost of centering, shuttering, finishing and reinforcement - All work up to plinth level: 1:1:5:3 (1 cement 1.5 coarse sand :3 graded stone aggregate 20 mm nominal size (Code: 5.1.2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -79,10 +86,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,7 +397,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -398,11 +406,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B1" s="1">
         <v>0.24</v>
@@ -410,7 +421,7 @@
     </row>
     <row r="2" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
@@ -418,7 +429,7 @@
     </row>
     <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>9.73</v>
@@ -426,7 +437,7 @@
     </row>
     <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>9.73</v>
@@ -434,7 +445,7 @@
     </row>
     <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>0.5</v>
@@ -442,7 +453,7 @@
     </row>
     <row r="6" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -450,7 +461,7 @@
     </row>
     <row r="7" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -458,7 +469,7 @@
     </row>
     <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>0.5</v>
